--- a/trunk/top/Qijia/齐家接口数据库设计.xlsx
+++ b/trunk/top/Qijia/齐家接口数据库设计.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="95">
   <si>
     <t>nick</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -390,6 +390,18 @@
   </si>
   <si>
     <t>varchar(250)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ErrInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(250)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1351,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.125" customWidth="1"/>
@@ -1403,6 +1415,17 @@
         <v>89</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trunk/top/Qijia/齐家接口数据库设计.xlsx
+++ b/trunk/top/Qijia/齐家接口数据库设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="15480" windowHeight="9120" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="15480" windowHeight="9120" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Jia_Shop(齐家店铺表)" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="102">
   <si>
     <t>nick</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -305,10 +305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>｛"名称":"实木地板","规格"："100*100"｝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>itemid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,6 +398,37 @@
   </si>
   <si>
     <t>错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UglyTplHtml</t>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过期模板内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharText</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(500)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{名称:实木地板{,}规格：100*100}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{text1:实木地板{,}text2：萨分散}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模板文字(标签不确定)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -810,7 +837,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -844,10 +871,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -855,10 +882,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -886,7 +913,21 @@
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +952,7 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
         <v>23</v>
@@ -933,7 +974,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -944,7 +985,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -970,9 +1011,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="23.875" customWidth="1"/>
   </cols>
@@ -982,7 +1024,7 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
         <v>30</v>
@@ -1045,13 +1087,13 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1059,10 +1101,21 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1087,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
         <v>50</v>
@@ -1106,7 +1159,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -1195,7 +1248,7 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
         <v>30</v>
@@ -1225,10 +1278,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
         <v>83</v>
-      </c>
-      <c r="B4" t="s">
-        <v>84</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -1252,13 +1305,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1288,7 +1341,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -1313,21 +1366,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
         <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
@@ -1335,24 +1388,24 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1373,21 +1426,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
@@ -1395,35 +1448,35 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
         <v>92</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
